--- a/JsonConverter/ExcelFiles/DNFieldObject.xlsx
+++ b/JsonConverter/ExcelFiles/DNFieldObject.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fileVersion appName="HCell" lastEdited="12.0" lowestEdited="12.0" rupBuild="0.535"/>
+  <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\UnityBasic_6\JsonConverter\ExcelFiles\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294934950" windowHeight="6150"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11700"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -19,112 +14,124 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
+  <x:si>
+    <x:t>2DPrefab/Harvest_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/Harvest_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_Gold</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드랍된 금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,1000</x:t>
+  </x:si>
   <x:si>
     <x:t>Harvest</x:t>
   </x:si>
   <x:si>
-    <x:t>10,1000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드랍된 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
     <x:t>Name</x:t>
   </x:si>
   <x:si>
+    <x:t>DropCountRange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropItemDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 설명 (도감용)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우선 프리팹으로 구현하자!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>harv_potate_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FieldObjectType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>harv_pizza_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
     <x:t>캐릭터 고유 ID</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>harv_potate_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FieldObjectType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 설명 (도감용)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropCountRange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우선 프리팹으로 구현하자!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropItemDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금화</x:t>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필드 채집용 옥수수</x:t>
   </x:si>
   <x:si>
     <x:t>DropItem</x:t>
   </x:si>
   <x:si>
+    <x:t>필드 채집용 감자</x:t>
+  </x:si>
+  <x:si>
     <x:t>harv_corn_1</x:t>
   </x:si>
   <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필드 채집용 옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필드 채집용 감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/Harvest_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_Gold</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/Harvest_Corn</x:t>
+    <x:t>피자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Pizza_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파인애플이 올려진 피자</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="9">
+  <x:fonts count="10">
     <x:font>
       <x:name val="Arial"/>
       <x:sz val="10"/>
@@ -156,6 +163,11 @@
       <x:color rgb="ff000000"/>
     </x:font>
     <x:font>
+      <x:name val="돋움"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
       <x:name val="&quot;맑은 고딕&quot;"/>
       <x:sz val="10"/>
       <x:color rgb="ff000000"/>
@@ -181,7 +193,6 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffffffff"/>
-        <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -211,7 +222,6 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffd2f2db"/>
-        <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -223,12 +233,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffffff00"/>
-        <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
   <x:borders count="3">
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left>
         <x:color rgb="ff000000"/>
       </x:left>
@@ -236,27 +245,33 @@
         <x:color rgb="ff000000"/>
       </x:right>
       <x:top>
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:top>
       <x:bottom>
         <x:color rgb="ff000000"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left style="thin">
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:left>
       <x:right style="thin">
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:right>
       <x:top style="thin">
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left style="thin">
         <x:color rgb="ff000000"/>
       </x:left>
@@ -269,10 +284,55 @@
       <x:bottom style="thin">
         <x:color rgb="ff000000"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="1">
+  <x:cellStyleXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -280,25 +340,25 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -313,7 +373,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -325,25 +385,25 @@
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="49" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="49" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="49" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="49" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="49" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="49" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="49" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -355,10 +415,10 @@
     <x:xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="49" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="49" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -366,15 +426,14 @@
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
-    <x:cellStyle name="표준" xfId="0" builtinId="0"/>
+    <x:cellStyle xfId="0" builtinId="0"/>
   </x:cellStyles>
-  <x:dxfs count="12">
+  <x:dxfs count="30">
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -457,7 +516,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -492,7 +550,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -537,7 +594,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -581,7 +637,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -589,10 +644,10 @@
           </x:font>
           <x:border>
             <x:left>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:left>
             <x:right>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:right>
             <x:top style="medium">
               <x:color rgb="ff6182d6"/>
@@ -601,10 +656,10 @@
               <x:color rgb="ff6182d6"/>
             </x:bottom>
             <x:vertical>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:vertical>
             <x:horizontal>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:horizontal>
           </x:border>
         </x:dxf>
@@ -616,10 +671,10 @@
           </x:font>
           <x:border>
             <x:left>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:left>
             <x:right>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:right>
             <x:top style="medium">
               <x:color rgb="ff6182d6"/>
@@ -628,10 +683,10 @@
               <x:color rgb="ff6182d6"/>
             </x:bottom>
             <x:vertical>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:vertical>
             <x:horizontal>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:horizontal>
           </x:border>
         </x:dxf>
@@ -666,7 +721,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -687,7 +741,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -718,15 +771,52 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
             <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
             <hs:offset val="0"/>
           </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd9e6fd"/>
+              <x:bgColor rgb="ffd9e6fd"/>
+            </x:patternFill>
+          </x:fill>
           <x:border>
-            <x:bottom style="medium">
-              <x:color rgb="ff6182d6"/>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
             </x:bottom>
           </x:border>
         </x:dxf>
@@ -734,16 +824,429 @@
       <mc:Fallback>
         <x:dxf>
           <x:font>
-            <x:b val="1"/>
-          </x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd9e6fd"/>
+              <x:bgColor rgb="ffd9e6fd"/>
+            </x:patternFill>
+          </x:fill>
           <x:border>
-            <x:bottom style="medium">
-              <x:color rgb="ff6182d6"/>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
             </x:bottom>
           </x:border>
         </x:dxf>
       </mc:Fallback>
     </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd9e6fd"/>
+              <x:bgColor rgb="ffd9e6fd"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd9e6fd"/>
+              <x:bgColor rgb="ffd9e6fd"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9d9d9"/>
+          <x:bgColor rgb="ffd9d9d9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9d9d9"/>
+          <x:bgColor rgb="ffd9d9d9"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:left style="thin">
+          <x:color rgb="ffbfbfbf"/>
+        </x:left>
+        <x:right style="thin">
+          <x:color rgb="ffbfbfbf"/>
+        </x:right>
+      </x:border>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9d9d9"/>
+          <x:bgColor rgb="ffd9d9d9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff4285f4"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff4285f4"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff4285f4"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff4285f4"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9e6fd"/>
+          <x:bgColor rgb="ffd9e6fd"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:bottom style="thin">
+          <x:color rgb="ff8db6f9"/>
+        </x:bottom>
+      </x:border>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9e6fd"/>
+          <x:bgColor rgb="ffd9e6fd"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:bottom style="thin">
+          <x:color rgb="ff8db6f9"/>
+        </x:bottom>
+      </x:border>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+            <x:horizontal style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+          </x:font>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+            <x:horizontal style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff4285f4"/>
+              <x:bgColor rgb="ff4285f4"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff4285f4"/>
+              <x:bgColor rgb="ff4285f4"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:top style="double">
+              <x:color rgb="ff4285f4"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:top style="double">
+              <x:color rgb="ff4285f4"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9e6fd"/>
+          <x:bgColor rgb="ffd9e6fd"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9e6fd"/>
+          <x:bgColor rgb="ffd9e6fd"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
   </x:dxfs>
   <x:tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <x:tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
@@ -772,7 +1275,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Sheets">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -967,9 +1470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr codeName="Sheet1">
-    <x:outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
-  </x:sheetPr>
+  <x:sheetPr codeName="Sheet1"/>
   <x:dimension ref="A1:R34"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
@@ -985,96 +1486,96 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
       <x:c r="D1" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E1" s="18"/>
       <x:c r="F1" s="18"/>
       <x:c r="G1" s="2"/>
       <x:c r="H1" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:9" ht="13.19999999999999928946">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:9" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E2" s="18" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E2" s="18" t="s">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="F2" s="18" t="s">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:9" s="13" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D3" s="12" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E3" s="19" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E3" s="19" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="F3" s="19" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G3" s="14" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H3" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I3" s="15"/>
     </x:row>
     <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E4" s="20" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F4" s="20" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G4" s="5"/>
       <x:c r="H4" s="5" t="s">
-        <x:v>32</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="16"/>
       <x:c r="J4" s="5"/>
@@ -1089,26 +1590,26 @@
     </x:row>
     <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E5" s="21" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F5" s="21" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="D5" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E5" s="21" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F5" s="21" t="s">
-        <x:v>9</x:v>
       </x:c>
       <x:c r="G5" s="5"/>
       <x:c r="H5" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I5" s="5"/>
       <x:c r="J5" s="5"/>
@@ -1123,26 +1624,26 @@
     </x:row>
     <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="27" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="27" t="s">
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E6" s="20" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F6" s="26" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G6" s="5"/>
       <x:c r="H6" s="28" t="s">
-        <x:v>30</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I6" s="5"/>
       <x:c r="J6" s="5"/>
@@ -1156,14 +1657,28 @@
       <x:c r="R6" s="5"/>
     </x:row>
     <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A7" s="7"/>
-      <x:c r="B7" s="7"/>
-      <x:c r="C7" s="7"/>
-      <x:c r="D7" s="7"/>
-      <x:c r="E7" s="22"/>
-      <x:c r="F7" s="22"/>
+      <x:c r="A7" s="7" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C7" s="7" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D7" s="7" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E7" s="22" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F7" s="22" t="s">
+        <x:v>35</x:v>
+      </x:c>
       <x:c r="G7" s="5"/>
-      <x:c r="H7" s="5"/>
+      <x:c r="H7" s="5" t="s">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="I7" s="5"/>
       <x:c r="J7" s="5"/>
       <x:c r="K7" s="5"/>
@@ -2447,7 +2962,7 @@
     <x:row r="998" ht="15.75" customHeight="1"/>
     <x:row r="999" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69972223043441772461" right="0.69972223043441772461" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>